--- a/ig/DM_FINESS/ASS-A12-CorresMediaTypeCDANonStructure-XdsFormatCode-CISIS.xlsx
+++ b/ig/DM_FINESS/ASS-A12-CorresMediaTypeCDANonStructure-XdsFormatCode-CISIS.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30T16:03:38+00:00</t>
+    <t>2024-12-31T12:36:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
